--- a/competitive_analysis_report.xlsx
+++ b/competitive_analysis_report.xlsx
@@ -66,16 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -492,48 +489,67 @@
         <v>3200</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2358.62</v>
+        <v>2342.9</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Serbatoio Ml</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>200</v>
+        <v>0.4</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>700</v>
+        <v>1.6</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>308</v>
+        <v>1.12</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Serbatoio Ml</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>5020000</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>279530.56</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Price Eur</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B5" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C5" s="2" t="n">
         <v>289</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>62.26</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>47</v>
+      <c r="D5" s="2" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -547,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -606,10 +622,10 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.046</v>
+        <v>0.025</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -633,48 +649,21 @@
         <v>13</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.218</v>
+        <v>0.031</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tristar ST-8300 Ferro da stiro a vapore, 2000 W – </t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -688,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -716,26 +705,6 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Common Issues</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Tristar ST-8300 Ferro da stiro a vapore,</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>considerando, prezzo, avevo, poche, aspettative</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Considerando il prezzo avevo poche aspettative, però questo acquisto è stato una pura delusione. Spe</t>
         </is>
       </c>
     </row>
@@ -836,11 +805,19 @@
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1500</v>
+      </c>
       <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="I2" s="2" t="n">
+        <v>120</v>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -865,11 +842,19 @@
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>1500</v>
+      </c>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
+      <c r="I3" s="2" t="n">
+        <v>140</v>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -895,12 +880,18 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
+        <v>1830</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1500</v>
+      </c>
       <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
+      <c r="I4" s="2" t="n">
+        <v>140</v>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -928,10 +919,16 @@
       <c r="E5" s="2" t="n">
         <v>2800</v>
       </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="F5" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>300</v>
+      </c>
       <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
+      <c r="I5" s="2" t="n">
+        <v>250</v>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -959,10 +956,16 @@
       <c r="E6" s="2" t="n">
         <v>2200</v>
       </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
+      <c r="F6" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1500</v>
+      </c>
       <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="I6" s="2" t="n">
+        <v>140</v>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -993,7 +996,9 @@
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
+      <c r="I7" s="2" t="n">
+        <v>120</v>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1008,23 +1013,25 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Imetec ZeroCalc Z1 2800 – Ferro da stiro a vapore 2200W</t>
+          <t>Stiratore Verticale, 40 g/min, Ferro da Stiro 2 in 1, Serbat</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>2200</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
+      <c r="G8" s="2" t="n">
+        <v>350</v>
+      </c>
       <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
+      <c r="I8" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1032,14 +1039,14 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Imetec-Tecnologia-Anticalcare-Scorrevolezza-Energetico/dp/</t>
+          <t>https://www.amazon.it/Stiratore-Verticale-Ferro-Stiro-Serbatoio/dp/B0H1WCMLQB/re</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rowenta DX1635 Effective + Ferro da Stiro a Vapore, 2400 W, </t>
+          <t>Imetec ZeroCalc Z1 2800 – Ferro da stiro a vapore 2200W</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1050,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
@@ -1063,7 +1070,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/FERRO-VAPORE-ROWENTA-EFFECTIVE-DX1635D1/dp/B08H4MGC8T/ref=</t>
+          <t>https://www.amazon.it/Imetec-Tecnologia-Anticalcare-Scorrevolezza-Energetico/dp/</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1093,9 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
+      <c r="I10" s="2" t="n">
+        <v>210</v>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1101,21 +1110,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rowenta Freemove Force, Ferro da Stiro a Vapore Senza Filo, </t>
+          <t xml:space="preserve">Rowenta DX1635 Effective + Ferro da Stiro a Vapore, 2400 W, </t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="2" t="n"/>
+      <c r="E11" s="2" t="n">
+        <v>2400</v>
+      </c>
       <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
+      <c r="G11" s="2" t="n">
+        <v>250</v>
+      </c>
       <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
+      <c r="I11" s="2" t="n">
+        <v>120</v>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1123,18 +1138,18 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Rowenta-Efficiente-Riscaldamento-Spegnimento-DE6720D1/dp/B</t>
+          <t>https://www.amazon.it/FERRO-VAPORE-ROWENTA-EFFECTIVE-DX1635D1/dp/B08H4MGC8T/ref=</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Rowenta PRO Master Ferro da Stiro a Vapore, Azzurro, DW8215</t>
+          <t xml:space="preserve">Rowenta Freemove Force, Ferro da Stiro a Vapore Senza Filo, </t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
@@ -1144,7 +1159,9 @@
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
+      <c r="I12" s="2" t="n">
+        <v>35</v>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1152,18 +1169,18 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Rowenta-DW8215-vapore-Microsteam-soleplate/dp/B07CZJKNDM/r</t>
+          <t>https://www.amazon.it/Rowenta-Efficiente-Riscaldamento-Spegnimento-DE6720D1/dp/B</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Rowenta Focus Excel, Ferro da Stiro a Vapore, DW5325</t>
+          <t>Rowenta PRO Master Ferro da Stiro a Vapore, Azzurro, DW8215</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
@@ -1181,26 +1198,24 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Rowenta-Modalit%C3%A0-Piastra-Acciaio-Anticalcare/dp/B09C6</t>
+          <t>https://www.amazon.it/Rowenta-DW8215-vapore-Microsteam-soleplate/dp/B07CZJKNDM/r</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Rowenta DX1531 Effective 2 Ferro da Stiro a Vapore, Anticalc</t>
+          <t>Rowenta Focus Excel, Ferro da Stiro a Vapore, DW5325</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>2200</v>
-      </c>
+      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
@@ -1212,28 +1227,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Rowenta-DX1531D1-Ferro-Vapore-Effective/dp/B07SBCZMN7/ref=</t>
+          <t>https://www.amazon.it/Rowenta-Modalit%C3%A0-Piastra-Acciaio-Anticalcare/dp/B09C6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Rowenta Force Pro 300, Ferro da Stiro con Generatore di Vapo</t>
+          <t>Rowenta DX1531 Effective 2 Ferro da Stiro a Vapore, Anticalc</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="2" t="n"/>
+      <c r="E15" s="2" t="n">
+        <v>2200</v>
+      </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
+      <c r="I15" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1241,18 +1260,18 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Rowenta-Force-Generatore-Vapore-VR5430/dp/B0GTWGYV1J/ref=s</t>
+          <t>https://www.amazon.it/Rowenta-DX1531D1-Ferro-Vapore-Effective/dp/B07SBCZMN7/ref=</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Rowenta Eco Intelligence Ferro a Vapore, Nero/Verde, DW6330</t>
+          <t>Rowenta Force Pro 300, Ferro da Stiro con Generatore di Vapo</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
@@ -1270,18 +1289,18 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Rowenta-DW6330D1-Intelligence-Distribuzione-Riscaldmento/d</t>
+          <t>https://www.amazon.it/Rowenta-Force-Generatore-Vapore-VR5430/dp/B0GTWGYV1J/ref=s</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Rowenta Access Steam, Ferro da Stiro a Vapore, DW4301</t>
+          <t>Rowenta Eco Intelligence Ferro a Vapore, Nero/Verde, DW6330</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
@@ -1299,18 +1318,18 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Rowenta-DW4301D1-Microsteam-Anticalcare-Precisione/dp/B0B9</t>
+          <t>https://www.amazon.it/Rowenta-DW6330D1-Intelligence-Distribuzione-Riscaldmento/d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Polti Vaporella Quick&amp;Comfort QC120, Ferro da Stiro a Vapore</t>
+          <t>Rowenta Access Steam, Ferro da Stiro a Vapore, DW4301</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
@@ -1328,26 +1347,24 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Polti-Vaporella-Inossidabile-Impugnatura-Cuscinetto/dp/B09</t>
+          <t>https://www.amazon.it/Rowenta-DW4301D1-Microsteam-Anticalcare-Precisione/dp/B0B9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Imetec ZeroCalc VPR-X – Ferro da stiro a vapore 2600W</t>
+          <t>Polti Vaporella Quick&amp;Comfort QC120, Ferro da Stiro a Vapore</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>2600</v>
-      </c>
+      <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
@@ -1359,30 +1376,28 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Imetec-Zerocalc-VPR-X-anticalcare-precisione/dp/B0FWRNLSL6</t>
+          <t>https://www.amazon.it/Polti-Vaporella-Inossidabile-Impugnatura-Cuscinetto/dp/B09</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Braun TexStyle 1 SI1029BL, Ferro da Stiro Antiaderente, 120g</t>
+          <t>Imetec ZeroCalc VPR-X – Ferro da stiro a vapore 2600W</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1900</v>
+        <v>2600</v>
       </c>
       <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n">
-        <v>220</v>
-      </c>
+      <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="inlineStr">
@@ -1392,28 +1407,34 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Braun-SI1029BL-Antiaderente-Riscaldamento-Rubinetto/dp/B0F</t>
+          <t>https://www.amazon.it/Imetec-Zerocalc-VPR-X-anticalcare-precisione/dp/B0FWRNLSL6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Polti Vaporella Simply VS10.10, Ferro Da Stiro Generatore di</t>
+          <t>Braun TexStyle 1 SI1029BL, Ferro da Stiro Antiaderente, 120g</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="2" t="n"/>
+      <c r="E21" s="2" t="n">
+        <v>1900</v>
+      </c>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
+      <c r="G21" s="2" t="n">
+        <v>220</v>
+      </c>
       <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
+      <c r="I21" s="2" t="n">
+        <v>120</v>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1421,26 +1442,24 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Polti-Vaporella-Generatore-Serbatoio-Estraibile/dp/B07FZK5</t>
+          <t>https://www.amazon.it/Braun-SI1029BL-Antiaderente-Riscaldamento-Rubinetto/dp/B0F</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Philips 5000 Ferro da Stiro a Vapore, 2400 W, Colpo Vapore 1</t>
+          <t>Polti Vaporella Simply VS10.10, Ferro Da Stiro Generatore di</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>2400</v>
-      </c>
+      <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
@@ -1452,7 +1471,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Philips-5000-DST5030-80-prestazioni/dp/B08TJ1Z1NP/ref=sr_1</t>
+          <t>https://www.amazon.it/Polti-Vaporella-Generatore-Serbatoio-Estraibile/dp/B07FZK5</t>
         </is>
       </c>
     </row>
@@ -1473,11 +1492,11 @@
         <v>2000</v>
       </c>
       <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n">
-        <v>230</v>
-      </c>
+      <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
+      <c r="I23" s="2" t="n">
+        <v>90</v>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1492,25 +1511,25 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Amazon Basics Ferro da Stiro a Vapore con Piastra Antiaderen</t>
+          <t>Philips 5000 Ferro da Stiro a Vapore, 2400 W, Colpo Vapore 1</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n">
-        <v>200</v>
-      </c>
+      <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
+      <c r="I24" s="2" t="n">
+        <v>180</v>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1518,32 +1537,34 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Amazon-Basics-antiaderente-autopulente-Dimensioni/dp/B0DVS</t>
+          <t>https://www.amazon.it/Philips-5000-DST5030-80-prestazioni/dp/B08TJ1Z1NP/ref=sr_1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Braun FreeStyle3 FI3124PU Ferro da Stiro con 5 Anni di Assis</t>
+          <t>Amazon Basics Ferro da Stiro a Vapore con Piastra Antiaderen</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2700</v>
+        <v>1800</v>
       </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
+      <c r="I25" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1551,30 +1572,34 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Braun-FI3124PU-Assistenza-SuperCeramic-Spegnimento/dp/B0BZ</t>
+          <t>https://www.amazon.it/Amazon-Basics-antiaderente-autopulente-Dimensioni/dp/B0DVS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Rowenta VR5020 Liberty Ferro da Stiro con Generatore di Vapo</t>
+          <t>Braun FreeStyle3 FI3124PU Ferro da Stiro con 5 Anni di Assis</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2200</v>
+        <v>2700</v>
       </c>
       <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
+      <c r="G26" s="2" t="n">
+        <v>270</v>
+      </c>
       <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
+      <c r="I26" s="2" t="n">
+        <v>170</v>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1582,28 +1607,34 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Rowenta-VR5020-Liberty-Generatore-Potente/dp/B07MCDHM8Q/re</t>
+          <t>https://www.amazon.it/Braun-FI3124PU-Assistenza-SuperCeramic-Spegnimento/dp/B0BZ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Polti Vaporella Simply VS10.12, Ferro da Stiro Generatore di</t>
+          <t>Rowenta VR5020 Liberty Ferro da Stiro con Generatore di Vapo</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="2" t="n"/>
+      <c r="E27" s="2" t="n">
+        <v>2200</v>
+      </c>
       <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
+      <c r="G27" s="2" t="n">
+        <v>5020000</v>
+      </c>
       <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
+      <c r="I27" s="2" t="n">
+        <v>200</v>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1611,18 +1642,18 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Polti-Vaporella-Generatore-Serbatoio-Estraibile/dp/B07FZ3V</t>
+          <t>https://www.amazon.it/Rowenta-VR5020-Liberty-Generatore-Potente/dp/B07MCDHM8Q/re</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Rowenta Force Pro 300, Ferro con Generatore di Vapore, Acqua</t>
+          <t>Polti Vaporella Simply VS10.12, Ferro da Stiro Generatore di</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
@@ -1640,26 +1671,24 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Rowenta-Force-Generatore-Vapore-VR5431/dp/B0GJTRLJPR/ref=s</t>
+          <t>https://www.amazon.it/Polti-Vaporella-Generatore-Serbatoio-Estraibile/dp/B07FZ3V</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Philips PerfectCare 6000 Ferro da Stiro con Caldaia, 6.5 Bar</t>
+          <t>Rowenta Force Pro 300, Ferro con Generatore di Vapore, Acqua</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>2400</v>
-      </c>
+      <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="n"/>
@@ -1671,28 +1700,34 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Philips-PerfectCare-Serie-Ferro-Caldaia/dp/B0GPR83DT9/ref=</t>
+          <t>https://www.amazon.it/Rowenta-Force-Generatore-Vapore-VR5431/dp/B0GJTRLJPR/ref=s</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Rowenta Ferro da Stiro Express Steam DW4345D1, Rosa</t>
+          <t>Philips PerfectCare 6000 Ferro da Stiro con Caldaia, 6.5 Bar</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>44</v>
+        <v>179</v>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="2" t="n"/>
+      <c r="E30" s="2" t="n">
+        <v>2400</v>
+      </c>
       <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
+      <c r="G30" s="2" t="n">
+        <v>1800</v>
+      </c>
       <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
+      <c r="I30" s="2" t="n">
+        <v>500</v>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1700,18 +1735,18 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/ROWENTA-FERRO-STIRO-EXPRESS-DW4345D1/dp/B08H8RKD3B/ref=sr_</t>
+          <t>https://www.amazon.it/Philips-PerfectCare-Serie-Ferro-Caldaia/dp/B0GPR83DT9/ref=</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Polti Vaporella 505 Pro, Ferro da Stiro a Vapore con Caldaia</t>
+          <t>ODS-44152 Ferro da Stiro con sensore per attivare luci e Suo</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
@@ -1729,18 +1764,18 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Polti-Vaporella-Vapore-Caldaia-Sicurezza/dp/B00D7ARYHC/ref</t>
+          <t>https://www.amazon.it/ODS-44152-Ferro-sensore-attivare-44152/dp/B08S47S8X8/ref=s</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ODS-44152 Ferro da Stiro con sensore per attivare luci e Suo</t>
+          <t>Rowenta Ferro da Stiro Express Steam DW4345D1, Rosa</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
@@ -1758,24 +1793,24 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/ODS-44152-Ferro-sensore-attivare-44152/dp/B08S47S8X8/ref=s</t>
+          <t>https://www.amazon.it/ROWENTA-FERRO-STIRO-EXPRESS-DW4345D1/dp/B08H8RKD3B/ref=sr_</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Ariete Steam Iron 2000W 2000 W 28 g/min</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n"/>
+          <t>Polti Vaporella 505 Pro, Ferro da Stiro a Vapore con Caldaia</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>94</v>
+      </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>2000</v>
-      </c>
+      <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
@@ -1787,30 +1822,30 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Steam-Iron-2000W-2000-min/dp/B01FSGA3FC/ref=sr_1_32?dib=ey</t>
+          <t>https://www.amazon.it/Polti-Vaporella-Vapore-Caldaia-Sicurezza/dp/B00D7ARYHC/ref</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Philips Azur 8000 Ferro da Stiro a Vapore, 3000 W, Colpo Vap</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>65</v>
-      </c>
+          <t>Ariete Steam Iron 2000W 2000 W 28 g/min</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
+      <c r="I34" s="2" t="n">
+        <v>28</v>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1818,7 +1853,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Philips-Azur-Serie-Ferro-Vapore/dp/B0B7KCK2YV/ref=sr_1_33?</t>
+          <t>https://www.amazon.it/Steam-Iron-2000W-2000-min/dp/B01FSGA3FC/ref=sr_1_33?dib=ey</t>
         </is>
       </c>
     </row>
@@ -1858,23 +1893,27 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>BLACK+DECKER - Ferro da stiro, 3000W, piastra ceramica, colp</t>
+          <t xml:space="preserve">SEVERIN BA 3243 Ferro da stiro a vapore e a secco 2400W con </t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
+      <c r="G36" s="2" t="n">
+        <v>200</v>
+      </c>
       <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
+      <c r="I36" s="2" t="n">
+        <v>70</v>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1882,32 +1921,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/BLACK-DECKER-piastra-ceramica-vapore/dp/B08V8G4YVD/ref=sr_</t>
+          <t>https://www.amazon.it/SEVERIN-serbatoio-autopulente-piastra-ceramica/dp/B003HDB1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rowenta De5010 Freemove Ferro da Stiro a Vapore senza Filo, </t>
+          <t>BLACK+DECKER - Ferro da stiro, 3000W, piastra ceramica, colp</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n">
-        <v>250</v>
-      </c>
+      <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
+      <c r="I37" s="2" t="n">
+        <v>200</v>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1915,32 +1954,30 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Rowenta-DE5010-Freemove-Ferro-Vapore/dp/B075FV7YW3/ref=sr_</t>
+          <t>https://www.amazon.it/BLACK-DECKER-piastra-ceramica-vapore/dp/B08V8G4YVD/ref=sr_</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEVERIN BA 3243 Ferro da stiro a vapore e a secco 2400W con </t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>28</v>
-      </c>
+          <t>Philips Azur 8000 Ferro da Stiro a Vapore, 3000 W, Colpo Vap</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n">
-        <v>200</v>
-      </c>
+      <c r="G38" s="2" t="n"/>
       <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
+      <c r="I38" s="2" t="n">
+        <v>240</v>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1948,32 +1985,34 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/SEVERIN-serbatoio-autopulente-piastra-ceramica/dp/B003HDB1</t>
+          <t>https://www.amazon.it/Philips-Azur-Serie-Ferro-Vapore/dp/B0B7KCK2YV/ref=sr_1_37?</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Braun TexStyle 9 SI9661VI Ferro da Stiro a Vapore con Tecnol</t>
+          <t xml:space="preserve">Rowenta De5010 Freemove Ferro da Stiro a Vapore senza Filo, </t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n">
-        <v>330</v>
+        <v>250</v>
       </c>
       <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
+      <c r="I39" s="2" t="n">
+        <v>120</v>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -1981,28 +2020,34 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Braun-SI9661VI-Assistenza-energetico-Superceramic/dp/B0CJY</t>
+          <t>https://www.amazon.it/Rowenta-DE5010-Freemove-Ferro-Vapore/dp/B075FV7YW3/ref=sr_</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Philips PerfectCare 7000 Ferro da Stiro con Caldaia, 8.5 Bar</t>
+          <t>Braun TexStyle 9 SI9661VI Ferro da Stiro a Vapore con Tecnol</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>269</v>
+        <v>89</v>
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="2" t="n"/>
+      <c r="E40" s="2" t="n">
+        <v>3200</v>
+      </c>
       <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
+      <c r="G40" s="2" t="n">
+        <v>330</v>
+      </c>
       <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
+      <c r="I40" s="2" t="n">
+        <v>260</v>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -2010,30 +2055,30 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Philips-PerfectCare-SteamGlide-PSG7200-60/dp/B0F5WP74RQ/re</t>
+          <t>https://www.amazon.it/Braun-SI9661VI-Assistenza-energetico-Superceramic/dp/B0CJY</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cecotec Ferro Da Stiro a Vapore Fast&amp;Furious 5040 Absolute. </t>
+          <t>Philips PerfectCare 7000 Ferro da Stiro con Caldaia, 8.5 Bar</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>3000</v>
-      </c>
+      <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
+      <c r="I41" s="2" t="n">
+        <v>600</v>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -2041,18 +2086,18 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Cecotec-Absolute-Modalit%C3%A0-Anti-goccia-anticalcare/dp/</t>
+          <t>https://www.amazon.it/Philips-PerfectCare-SteamGlide-PSG7200-60/dp/B0F5WP74RQ/re</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Rowenta Steamforce Pro, Ferro a Vapore, DW9520</t>
+          <t xml:space="preserve">Rowenta Silence Steam Pro, Ferro da Stiro Professionale con </t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>109</v>
+        <v>289</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
@@ -2070,30 +2115,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Rowenta-Steamforce-Anticalcare-Spegnimento-Intelligente/dp</t>
+          <t>https://www.amazon.it/Rowenta-Silence-Silenziosa-Prestazioni-Pressione/dp/B07H45</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Girmi ST91 Ferro da Stiro a Secco 900 W, Senza Vapore, Nero</t>
+          <t xml:space="preserve">Cecotec Ferro Da Stiro a Vapore Fast&amp;Furious 5040 Absolute. </t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>900</v>
+        <v>3000</v>
       </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
       <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
+      <c r="I43" s="2" t="n">
+        <v>65</v>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -2101,26 +2148,24 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Girmi-Ferro-Stiro-Secco-Unica/dp/B07W6JHFGC/ref=sr_1_42?di</t>
+          <t>https://www.amazon.it/Cecotec-Absolute-Modalit%C3%A0-Anti-goccia-anticalcare/dp/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>BLACK+DECKER - ferro da stiro a vapore 2200W | anticalcare |</t>
+          <t>Rowenta Steamforce Pro, Ferro a Vapore, DW9520</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>2200</v>
-      </c>
+      <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="n"/>
@@ -2132,24 +2177,26 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/BLACK-DECKER-Bxir2200E-Ferra-Plastica/dp/B07KFZ13XT/ref=sr</t>
+          <t>https://www.amazon.it/Rowenta-Steamforce-Anticalcare-Spegnimento-Intelligente/dp</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rowenta Silence Steam Pro, Ferro da Stiro Professionale con </t>
+          <t>Girmi ST91 Ferro da Stiro a Secco 900 W, Senza Vapore, Nero</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>289</v>
+        <v>32</v>
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="2" t="n"/>
+      <c r="E45" s="2" t="n">
+        <v>900</v>
+      </c>
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
@@ -2161,32 +2208,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Rowenta-Silence-Silenziosa-Prestazioni-Pressione/dp/B07H45</t>
+          <t>https://www.amazon.it/Girmi-Ferro-Stiro-Secco-Unica/dp/B07W6JHFGC/ref=sr_1_44?di</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Girmi ST6204 Ferro da Stiro a Vapore 2800W, Colpo Vapore 140</t>
+          <t>BLACK+DECKER - ferro da stiro a vapore 2200W | anticalcare |</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2800</v>
+        <v>2200</v>
       </c>
       <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n">
-        <v>380</v>
-      </c>
+      <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
+      <c r="I46" s="2" t="n">
+        <v>120</v>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -2194,7 +2241,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Girmi-Ferro-stiro-vapore-2800W/dp/B091DQ77SB/ref=sr_1_45?d</t>
+          <t>https://www.amazon.it/BLACK-DECKER-Bxir2200E-Ferra-Plastica/dp/B07KFZ13XT/ref=sr</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2266,9 @@
         <v>300</v>
       </c>
       <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
+      <c r="I47" s="2" t="n">
+        <v>25</v>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -2234,21 +2283,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Imetec Rapidvapor Plus – Ferro da stiro generatore di vapore</t>
+          <t>Girmi ST6204 Ferro da Stiro a Vapore 2800W, Colpo Vapore 140</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="2" t="n"/>
+      <c r="E48" s="2" t="n">
+        <v>2800</v>
+      </c>
       <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
+      <c r="G48" s="2" t="n">
+        <v>380</v>
+      </c>
       <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
+      <c r="I48" s="2" t="n">
+        <v>140</v>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
           <t>Amazon.it</t>
@@ -2256,7 +2311,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Imetec-Rapidvapor-Plus-generatore-rivestimento/dp/B0CVNCNY</t>
+          <t>https://www.amazon.it/Girmi-Ferro-stiro-vapore-2800W/dp/B091DQ77SB/ref=sr_1_47?d</t>
         </is>
       </c>
     </row>
